--- a/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECAF9C73-659C-4E14-B462-C49E81547A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAE0C606-CC74-451C-8C38-10759FC223ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1059,13 +1059,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S3aH2,S4aH2,S2aH2,S1aH2</t>
+    <t>S4aH2,S3aH2,S1aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH1,S2aH1,S2aH3,S3aH3,S4aH1,S1aH1,S4aH3,S1aH3</t>
+    <t>S2aH1,S2aH3,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH1,S2aH1,S2aH3,S3aH3,S4aH1,S1aH1,S4aH3,S1aH3</v>
+        <v>S2aH1,S2aH3,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S3aH2,S4aH2,S2aH2,S1aH2</v>
+        <v>S4aH2,S3aH2,S1aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1785,7 +1785,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54BA7E11-A1C6-47E1-9985-0BBDBA0D7AAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FAB175D-EC77-4C0B-8C9E-0CEC5929A60E}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1869,7 +1869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9B099A2-348E-4E80-8C4F-7A089A5A2BAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51FEB0A9-8A2D-416B-A827-06AA3E3ADFD3}">
   <dimension ref="B9:O718"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22211,7 +22211,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B12E434-8570-4D3A-830E-A4A4EA385117}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6E697CD-E761-4864-B86A-1359FBA8A37D}">
   <dimension ref="B9:BL141"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -35119,7 +35119,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE30699-BBD9-4738-A764-3EBD119BCE68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D4A7CC-9948-4F7A-9150-BA263E93E3D6}">
   <dimension ref="A9:S34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAE0C606-CC74-451C-8C38-10759FC223ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46BD6A5C-97DE-467B-86CB-D42D7975CAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1059,13 +1059,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S3aH2,S1aH2,S2aH2</t>
+    <t>S2aH2,S4aH2,S1aH2,S3aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH1,S2aH3,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</t>
+    <t>S2aH3,S3aH1,S3aH3,S4aH1,S2aH1,S1aH3,S1aH1,S4aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH1,S2aH3,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</v>
+        <v>S2aH3,S3aH1,S3aH3,S4aH1,S2aH1,S1aH3,S1aH1,S4aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S3aH2,S1aH2,S2aH2</v>
+        <v>S2aH2,S4aH2,S1aH2,S3aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1785,7 +1785,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FAB175D-EC77-4C0B-8C9E-0CEC5929A60E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B175A9B-A537-448C-9121-DE3B187A3EFB}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1869,7 +1869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51FEB0A9-8A2D-416B-A827-06AA3E3ADFD3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73682B63-FE1F-4FE6-93D5-322A7CE25782}">
   <dimension ref="B9:O718"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22211,7 +22211,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6E697CD-E761-4864-B86A-1359FBA8A37D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0081F6EE-7732-401E-B864-1EE301D362A9}">
   <dimension ref="B9:BL141"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -35119,7 +35119,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D4A7CC-9948-4F7A-9150-BA263E93E3D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB250439-2823-4956-A6AA-CA6644952106}">
   <dimension ref="A9:S34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_SAU_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46BD6A5C-97DE-467B-86CB-D42D7975CAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0CDFD10-E31B-4491-B619-887C2A3063D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1059,13 +1059,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S4aH2,S1aH2,S3aH2</t>
+    <t>S4aH2,S1aH2,S3aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S3aH1,S3aH3,S4aH1,S2aH1,S1aH3,S1aH1,S4aH3</t>
+    <t>S2aH1,S2aH3,S1aH3,S3aH1,S3aH3,S4aH1,S1aH1,S4aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S3aH1,S3aH3,S4aH1,S2aH1,S1aH3,S1aH1,S4aH3</v>
+        <v>S2aH1,S2aH3,S1aH3,S3aH1,S3aH3,S4aH1,S1aH1,S4aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S4aH2,S1aH2,S3aH2</v>
+        <v>S4aH2,S1aH2,S3aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1785,7 +1785,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B175A9B-A537-448C-9121-DE3B187A3EFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1C60C14-6DB0-4E0E-9072-E3FDAA720A09}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1869,7 +1869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73682B63-FE1F-4FE6-93D5-322A7CE25782}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38DB518A-F113-4351-9DAA-0CED8B079DD9}">
   <dimension ref="B9:O718"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22211,7 +22211,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0081F6EE-7732-401E-B864-1EE301D362A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F592C8D3-652D-4126-923B-797255460818}">
   <dimension ref="B9:BL141"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -35119,7 +35119,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB250439-2823-4956-A6AA-CA6644952106}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC4788E-8DD5-49A7-88B2-CE47775D8059}">
   <dimension ref="A9:S34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
